--- a/education_forms/023_oral_skills_assessment_form--education_forms.xlsx
+++ b/education_forms/023_oral_skills_assessment_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>section_1</t>
+          <t>pronunciation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Section 1</t>
+          <t>Pronunciation</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pronunciation</t>
+          <t>fluency</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pronunciation</t>
+          <t>Fluency</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fluency</t>
+          <t>vocabulary</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fluency</t>
+          <t>Vocabulary</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>vocabulary</t>
+          <t>comprehension</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>vocabulary</t>
+          <t>Comprehension</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>comprehension</t>
+          <t>interaction</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>comprehension</t>
+          <t>Interaction</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>interaction</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>interaction</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>section_2</t>
+          <t>pronunciation_skills</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Section 2</t>
+          <t>Pronunciation Skills</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>section_1</t>
+          <t>comprehension_areas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Section 1</t>
+          <t>Comprehension Areas</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>section_1</t>
+          <t>additional_skills</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Section 1</t>
+          <t>Additional Skills</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>section_1</t>
+          <t>pronunciation_challenges</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Section 1</t>
+          <t>Pronunciation Challenges</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>section_1</t>
+          <t>fluency_challenges</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Section 1</t>
+          <t>Fluency Challenges</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>section_1</t>
+          <t>comprehension_challenges</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Section 1</t>
+          <t>Comprehension Challenges</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>section_1</t>
+          <t>interaction_challenges</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Section 1</t>
+          <t>Interaction Challenges</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>section_1</t>
+          <t>additional_resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Section 1</t>
+          <t>Additional Resources</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>section_1</t>
+          <t>language_exchange</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Section 1</t>
+          <t>Language Exchange</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>section_1</t>
+          <t>self_assessment</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Section 1</t>
+          <t>Self-Assessment</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>section_1</t>
+          <t>feedback_from_others</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Section 1</t>
+          <t>Feedback from Others</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>section_1</t>
+          <t>recommendations</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Section 1</t>
+          <t>Recommendations</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -937,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -965,7 +965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>pronunciation_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -982,7 +982,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>pronunciation_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -999,7 +999,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>pronunciation_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1016,7 +1016,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>pronunciation_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1033,7 +1033,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>pronunciation_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1390,1020 +1390,952 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>section_2_choices</t>
+          <t>pronunciation_skills_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>accent</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Accent</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>section_2_choices</t>
+          <t>pronunciation_skills_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>articulation</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Articulation</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>section_2_choices</t>
+          <t>pronunciation_skills_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>inflection</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Inflection</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>section_2_choices</t>
+          <t>pronunciation_skills_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>intonation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Intonation</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>section_2_choices</t>
+          <t>pronunciation_skills_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>very_poor</t>
+          <t>vowel_sounds</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Very Poor</t>
+          <t>Vowel sounds</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>pronunciation_skills_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>consonant_sounds</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Consonant sounds</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>pronunciation_skills_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>fluency</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fluency</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>comprehension_areas_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>listening</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Listening</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>comprehension_areas_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>reading</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Reading</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>comprehension_areas_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>very_poor</t>
+          <t>writing</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Very Poor</t>
+          <t>Writing</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>comprehension_areas_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>speaking</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Speaking</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>additional_skills_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>grammar</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Grammar</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>additional_skills_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>pronunciation</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Pronunciation</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>additional_skills_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>vocabulary</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Vocabulary</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>additional_skills_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>very_poor</t>
+          <t>fluency</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Very Poor</t>
+          <t>Fluency</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>additional_skills_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>interaction</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Interaction</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>pronunciation_challenges_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>word_order</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Word order</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>pronunciation_challenges_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>syntactic_errors</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Syntactic errors</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>pronunciation_challenges_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>articulation_difficulties</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Articulation difficulties</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>pronunciation_challenges_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>very_poor</t>
+          <t>vowel_sounds</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Very Poor</t>
+          <t>Vowel sounds</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>pronunciation_challenges_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>consonant_sounds</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Consonant sounds</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>fluency_challenges_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>speed</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Speed</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>fluency_challenges_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>confidence</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Confidence</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>fluency_challenges_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>speaking_in_front_of_an_audience</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Speaking in front of an audience</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>fluency_challenges_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>very_poor</t>
+          <t>using_idiomatic_expressions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Very Poor</t>
+          <t>Using idiomatic expressions</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>fluency_challenges_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>understanding_nuances</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Understanding nuances</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>comprehension_challenges_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>reading_speed</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Reading speed</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>comprehension_challenges_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>vocabulary_building</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Vocabulary building</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>comprehension_challenges_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>contextual_understanding</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Contextual understanding</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>comprehension_challenges_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>very_poor</t>
+          <t>active_listening</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Very Poor</t>
+          <t>Active listening</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>comprehension_challenges_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>grammar_rules</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Grammar rules</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>interaction_challenges_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>engaging_in_conversations</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Engaging in conversations</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>interaction_challenges_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>understanding_idiomatic_expressions</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Understanding idiomatic expressions</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>interaction_challenges_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>asking_questions</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Asking questions</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>interaction_challenges_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>very_poor</t>
+          <t>giving_feedback</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Very Poor</t>
+          <t>Giving feedback</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>interaction_challenges_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>maintaining_eye_contact</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Maintaining eye contact</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>additional_resources_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>language_learning_apps</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Language learning apps</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>additional_resources_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>youtube_videos</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>YouTube videos</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>additional_resources_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>podcasts</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Podcasts</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>additional_resources_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>very_poor</t>
+          <t>language_exchange_websites</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Very Poor</t>
+          <t>Language exchange websites</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>additional_resources_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>language_learning_podcasts</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Language learning podcasts</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>language_exchange_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>language_exchange_websites</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Language exchange websites</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>language_exchange_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>language_exchange_apps</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Language exchange apps</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>language_exchange_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>language_exchange_events</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Language exchange events</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>language_exchange_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>very_poor</t>
+          <t>language_conversation_practice_with_a_tutor</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Very Poor</t>
+          <t>Language conversation practice with a tutor</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>language_exchange_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>language_conversation_groups</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Language conversation groups</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>self_assessment_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>self-assessment_1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Self-assessment 1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>self_assessment_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>self-assessment_2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Self-assessment 2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>self_assessment_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>self-assessment_3</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Self-assessment 3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>self_assessment_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>very_poor</t>
+          <t>self-assessment_4</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Very Poor</t>
+          <t>Self-assessment 4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>self_assessment_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>self-assessment_5</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Self-assessment 5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>feedback_from_others_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>feedback_from_language_teacher</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Feedback from language teacher</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>feedback_from_others_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>feedback_from_language_partner</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Feedback from language partner</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>feedback_from_others_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>feedback_from_family_member</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Feedback from family member</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>feedback_from_others_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>very_poor</t>
+          <t>feedback_from_friend</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Very Poor</t>
+          <t>Feedback from friend</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>feedback_from_others_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>feedback_from_self-reflection</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Excellent</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>section_1_choices</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>section_1_choices</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>average</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>section_1_choices</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>section_1_choices</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>very_poor</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Very Poor</t>
+          <t>Feedback from self-reflection</t>
         </is>
       </c>
     </row>
